--- a/Report/RSReport/NSE_500_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_500_Perception_Report.xlsx
@@ -4664,7 +4664,7 @@
         <v>90</v>
       </c>
       <c r="B83" s="1">
-        <v>2515</v>
+        <v>2512.5</v>
       </c>
       <c r="C83" s="2">
         <v>8.17</v>
@@ -22510,7 +22510,7 @@
         <v>51</v>
       </c>
       <c r="D2" s="2">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -22552,7 +22552,7 @@
         <v>65.2</v>
       </c>
       <c r="D5" s="2">
-        <v>61.4</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
